--- a/data/data_peulla/data_peulla.xlsx
+++ b/data/data_peulla/data_peulla.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\ST_abastecimiento\ST_abastecimiento\data\data_peulla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A12A61CF-7EE0-4F70-AD4B-286B6C016C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28418B2-B456-4A71-BE4C-DEA57D0D2208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ACCFC183-5542-44E4-BD53-7CA800D5B3FB}"/>
   </bookViews>
@@ -44,12 +44,6 @@
     <t>Listado Union</t>
   </si>
   <si>
-    <t xml:space="preserve">Cantidad Mensual </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cantidad Anual </t>
-  </si>
-  <si>
     <t>Tipo</t>
   </si>
   <si>
@@ -855,6 +849,12 @@
   </si>
   <si>
     <t>Yogurth</t>
+  </si>
+  <si>
+    <t>Cantidad Mensual</t>
+  </si>
+  <si>
+    <t>Cantidad Anual</t>
   </si>
 </sst>
 </file>
@@ -1489,24 +1489,24 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="4">
         <v>6</v>
@@ -1516,7 +1516,7 @@
         <v>72</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" s="6">
         <v>2023</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" s="8">
         <v>4</v>
@@ -1537,7 +1537,7 @@
         <v>48</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="6">
         <v>2022</v>
@@ -1545,10 +1545,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" s="10">
         <v>6</v>
@@ -1558,7 +1558,7 @@
         <v>72</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="6">
         <v>2024</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5" s="12">
         <v>4</v>
@@ -1579,7 +1579,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="6">
         <v>2025</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="13">
         <v>2</v>
@@ -1600,7 +1600,7 @@
         <v>24</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" s="6">
         <v>2022</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="15">
         <v>5</v>
@@ -1621,7 +1621,7 @@
         <v>60</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" s="6">
         <v>2024</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -1642,7 +1642,7 @@
         <v>24</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" s="6">
         <v>2025</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" s="19">
         <v>2</v>
@@ -1663,7 +1663,7 @@
         <v>24</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" s="6">
         <v>2023</v>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="13">
         <v>1</v>
@@ -1684,7 +1684,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F10" s="6">
         <v>2022</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" s="15">
         <v>3</v>
@@ -1705,7 +1705,7 @@
         <v>36</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F11" s="6">
         <v>2024</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C12" s="17">
         <v>4</v>
@@ -1726,7 +1726,7 @@
         <v>48</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" s="6">
         <v>2025</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
@@ -1747,7 +1747,7 @@
         <v>48</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F13" s="6">
         <v>2023</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" s="22">
         <v>1</v>
@@ -1768,7 +1768,7 @@
         <v>12</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F14" s="6">
         <v>2023</v>
@@ -1776,10 +1776,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15" s="23">
         <v>1</v>
@@ -1789,7 +1789,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F15" s="6">
         <v>2022</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C16" s="17">
         <v>1</v>
@@ -1810,7 +1810,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F16" s="6">
         <v>2025</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C17" s="13">
         <v>2</v>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F17" s="6">
         <v>2024</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C18" s="17">
         <v>1</v>
@@ -1852,7 +1852,7 @@
         <v>12</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F18" s="6">
         <v>2025</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" s="13">
         <v>1</v>
@@ -1873,7 +1873,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F19" s="6">
         <v>2024</v>
@@ -1881,10 +1881,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="25">
         <v>7</v>
@@ -1894,7 +1894,7 @@
         <v>84</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F20" s="6">
         <v>2025</v>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C21" s="22">
         <v>5</v>
@@ -1915,7 +1915,7 @@
         <v>60</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F21" s="6">
         <v>2023</v>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" s="26">
         <v>3</v>
@@ -1936,7 +1936,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F22" s="6">
         <v>2022</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C23" s="15">
         <v>7</v>
@@ -1957,7 +1957,7 @@
         <v>84</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" s="6">
         <v>2024</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24" s="22">
         <v>2</v>
@@ -1978,7 +1978,7 @@
         <v>24</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F24" s="6">
         <v>2023</v>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C25" s="26">
         <v>2</v>
@@ -1999,7 +1999,7 @@
         <v>24</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F25" s="6">
         <v>2022</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" s="4">
         <v>5</v>
@@ -2020,7 +2020,7 @@
         <v>60</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F26" s="6">
         <v>2023</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C27" s="8">
         <v>5</v>
@@ -2041,7 +2041,7 @@
         <v>60</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F27" s="6">
         <v>2022</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C28" s="10">
         <v>5</v>
@@ -2062,7 +2062,7 @@
         <v>60</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F28" s="6">
         <v>2024</v>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C29" s="25">
         <v>2</v>
@@ -2083,7 +2083,7 @@
         <v>24</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F29" s="6">
         <v>2025</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C30" s="15">
         <v>2</v>
@@ -2104,7 +2104,7 @@
         <v>24</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F30" s="6">
         <v>2024</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C31" s="12">
         <v>3</v>
@@ -2125,7 +2125,7 @@
         <v>36</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6">
         <v>2025</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C32" s="15">
         <v>14</v>
@@ -2146,7 +2146,7 @@
         <v>168</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F32" s="6">
         <v>2024</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C33" s="25">
         <v>30</v>
@@ -2167,7 +2167,7 @@
         <v>360</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F33" s="6">
         <v>2025</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C34" s="22">
         <v>6</v>
@@ -2188,7 +2188,7 @@
         <v>72</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F34" s="6">
         <v>2023</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C35" s="26">
         <v>3</v>
@@ -2209,7 +2209,7 @@
         <v>36</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F35" s="6">
         <v>2022</v>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C36" s="15">
         <v>8</v>
@@ -2230,7 +2230,7 @@
         <v>96</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F36" s="6">
         <v>2024</v>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C37" s="25">
         <v>8</v>
@@ -2251,7 +2251,7 @@
         <v>96</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F37" s="6">
         <v>2025</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C38" s="22">
         <v>13</v>
@@ -2272,7 +2272,7 @@
         <v>156</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F38" s="6">
         <v>2023</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C39" s="26">
         <v>10</v>
@@ -2293,7 +2293,7 @@
         <v>120</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F39" s="6">
         <v>2022</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C40" s="15">
         <v>18</v>
@@ -2314,7 +2314,7 @@
         <v>216</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F40" s="6">
         <v>2024</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" s="25">
         <v>1</v>
@@ -2335,7 +2335,7 @@
         <v>12</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F41" s="6">
         <v>2025</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C42" s="26">
         <v>3</v>
@@ -2356,7 +2356,7 @@
         <v>36</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F42" s="6">
         <v>2024</v>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C43" s="25">
         <v>15</v>
@@ -2377,7 +2377,7 @@
         <v>180</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F43" s="6">
         <v>2025</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C44" s="26">
         <v>1</v>
@@ -2398,7 +2398,7 @@
         <v>12</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F44" s="6">
         <v>2024</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C45" s="25">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         <v>12</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F45" s="6">
         <v>2025</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C46" s="22">
         <v>12</v>
@@ -2440,7 +2440,7 @@
         <v>144</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F46" s="6">
         <v>2023</v>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C47" s="25">
         <v>13</v>
@@ -2461,7 +2461,7 @@
         <v>156</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F47" s="6">
         <v>2025</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C48" s="26">
         <v>11</v>
@@ -2482,7 +2482,7 @@
         <v>132</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F48" s="6">
         <v>2024</v>
@@ -2490,10 +2490,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C49" s="17">
         <v>6</v>
@@ -2503,7 +2503,7 @@
         <v>72</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F49" s="6">
         <v>2025</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C50" s="19">
         <v>1</v>
@@ -2524,7 +2524,7 @@
         <v>12</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F50" s="6">
         <v>2023</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C51" s="27">
         <v>4</v>
@@ -2545,7 +2545,7 @@
         <v>48</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F51" s="6">
         <v>2024</v>
@@ -2553,10 +2553,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C52" s="22">
         <v>5</v>
@@ -2566,7 +2566,7 @@
         <v>60</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F52" s="6">
         <v>2023</v>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C53" s="4">
         <v>3</v>
@@ -2587,7 +2587,7 @@
         <v>36</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F53" s="6">
         <v>2023</v>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C54" s="8">
         <v>3</v>
@@ -2608,7 +2608,7 @@
         <v>36</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F54" s="6">
         <v>2022</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C55" s="10">
         <v>3</v>
@@ -2629,7 +2629,7 @@
         <v>36</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F55" s="6">
         <v>2024</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C56" s="12">
         <v>3</v>
@@ -2650,7 +2650,7 @@
         <v>36</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F56" s="6">
         <v>2025</v>
@@ -2658,10 +2658,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C57" s="12">
         <v>4</v>
@@ -2671,7 +2671,7 @@
         <v>48</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F57" s="6">
         <v>2025</v>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C58" s="4">
         <v>3</v>
@@ -2692,7 +2692,7 @@
         <v>36</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F58" s="6">
         <v>2023</v>
@@ -2700,10 +2700,10 @@
     </row>
     <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C59" s="8">
         <v>3</v>
@@ -2713,7 +2713,7 @@
         <v>36</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F59" s="6">
         <v>2022</v>
@@ -2721,10 +2721,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C60" s="10">
         <v>3</v>
@@ -2734,7 +2734,7 @@
         <v>36</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F60" s="6">
         <v>2024</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C61" s="15">
         <v>5</v>
@@ -2755,7 +2755,7 @@
         <v>60</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F61" s="6">
         <v>2024</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C62" s="17">
         <v>5</v>
@@ -2776,7 +2776,7 @@
         <v>60</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F62" s="6">
         <v>2025</v>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C63" s="22">
         <v>6</v>
@@ -2797,7 +2797,7 @@
         <v>72</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F63" s="6">
         <v>2023</v>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C64" s="26">
         <v>3</v>
@@ -2818,7 +2818,7 @@
         <v>36</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F64" s="6">
         <v>2022</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C65" s="17">
         <v>2</v>
@@ -2839,7 +2839,7 @@
         <v>24</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F65" s="6">
         <v>2025</v>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C66" s="15">
         <v>3</v>
@@ -2860,7 +2860,7 @@
         <v>36</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F66" s="6">
         <v>2024</v>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C67" s="4">
         <v>5</v>
@@ -2881,7 +2881,7 @@
         <v>60</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F67" s="6">
         <v>2023</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C68" s="8">
         <v>5</v>
@@ -2902,7 +2902,7 @@
         <v>60</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F68" s="6">
         <v>2022</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C69" s="10">
         <v>5</v>
@@ -2923,7 +2923,7 @@
         <v>60</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F69" s="6">
         <v>2024</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C70" s="12">
         <v>4</v>
@@ -2944,7 +2944,7 @@
         <v>48</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F70" s="6">
         <v>2025</v>
@@ -2952,10 +2952,10 @@
     </row>
     <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C71" s="8">
         <v>2</v>
@@ -2965,7 +2965,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F71" s="6">
         <v>2022</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C72" s="10">
         <v>2</v>
@@ -2986,7 +2986,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F72" s="6">
         <v>2024</v>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C73" s="4">
         <v>2</v>
@@ -3007,7 +3007,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F73" s="6">
         <v>2023</v>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C74" s="28">
         <v>3</v>
@@ -3028,7 +3028,7 @@
         <v>36</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F74" s="6">
         <v>2025</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C75" s="12">
         <v>2</v>
@@ -3049,7 +3049,7 @@
         <v>24</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F75" s="6">
         <v>2025</v>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C76" s="4">
         <v>3</v>
@@ -3070,7 +3070,7 @@
         <v>36</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F76" s="6">
         <v>2023</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C77" s="8">
         <v>3</v>
@@ -3091,7 +3091,7 @@
         <v>36</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F77" s="6">
         <v>2022</v>
@@ -3099,10 +3099,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C78" s="10">
         <v>3</v>
@@ -3112,7 +3112,7 @@
         <v>36</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F78" s="6">
         <v>2024</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C79" s="12">
         <v>6</v>
@@ -3133,7 +3133,7 @@
         <v>72</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F79" s="6">
         <v>2025</v>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C80" s="4">
         <v>4</v>
@@ -3154,7 +3154,7 @@
         <v>48</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F80" s="6">
         <v>2023</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C81" s="8">
         <v>4</v>
@@ -3175,7 +3175,7 @@
         <v>48</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F81" s="6">
         <v>2022</v>
@@ -3183,10 +3183,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C82" s="10">
         <v>4</v>
@@ -3196,7 +3196,7 @@
         <v>48</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F82" s="6">
         <v>2024</v>
@@ -3204,10 +3204,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C83" s="17">
         <v>1</v>
@@ -3217,7 +3217,7 @@
         <v>12</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F83" s="6">
         <v>2025</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C84" s="26">
         <v>1</v>
@@ -3238,7 +3238,7 @@
         <v>12</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F84" s="6">
         <v>2024</v>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C85" s="22">
         <v>4</v>
@@ -3259,7 +3259,7 @@
         <v>48</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F85" s="6">
         <v>2023</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C86" s="29">
         <v>4</v>
@@ -3280,7 +3280,7 @@
         <v>48</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F86" s="6">
         <v>2022</v>
@@ -3288,10 +3288,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C87" s="30">
         <v>5</v>
@@ -3301,7 +3301,7 @@
         <v>60</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F87" s="6">
         <v>2024</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C88" s="17">
         <v>4</v>
@@ -3322,7 +3322,7 @@
         <v>48</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F88" s="6">
         <v>2025</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C89" s="22">
         <v>2</v>
@@ -3343,7 +3343,7 @@
         <v>24</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F89" s="6">
         <v>2023</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C90" s="29">
         <v>4</v>
@@ -3364,7 +3364,7 @@
         <v>48</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F90" s="6">
         <v>2022</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C91" s="30">
         <v>3</v>
@@ -3385,7 +3385,7 @@
         <v>36</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F91" s="6">
         <v>2024</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C92" s="17">
         <v>4</v>
@@ -3406,7 +3406,7 @@
         <v>48</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F92" s="6">
         <v>2025</v>
@@ -3414,10 +3414,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C93" s="31">
         <v>1</v>
@@ -3427,7 +3427,7 @@
         <v>12</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F93" s="6">
         <v>2023</v>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C94" s="23">
         <v>3</v>
@@ -3448,7 +3448,7 @@
         <v>36</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F94" s="6">
         <v>2022</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C95" s="10">
         <v>2</v>
@@ -3468,7 +3468,7 @@
         <v>24</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F95" s="6">
         <v>2024</v>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C96" s="25">
         <v>2</v>
@@ -3489,7 +3489,7 @@
         <v>24</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F96" s="6">
         <v>2025</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C97" s="25">
         <v>2</v>
@@ -3510,7 +3510,7 @@
         <v>24</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F97" s="6">
         <v>2025</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C98" s="17">
         <v>1</v>
@@ -3531,7 +3531,7 @@
         <v>12</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F98" s="6">
         <v>2025</v>
@@ -3539,10 +3539,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C99" s="29">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         <v>12</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F99" s="6">
         <v>2024</v>
@@ -3560,10 +3560,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C100" s="29">
         <v>2</v>
@@ -3573,7 +3573,7 @@
         <v>24</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F100" s="6">
         <v>2022</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C101" s="34">
         <v>2</v>
@@ -3594,7 +3594,7 @@
         <v>24</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F101" s="6">
         <v>2023</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C102" s="17">
         <v>3</v>
@@ -3615,7 +3615,7 @@
         <v>36</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F102" s="6">
         <v>2025</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C103" s="30">
         <v>3</v>
@@ -3636,7 +3636,7 @@
         <v>36</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F103" s="6">
         <v>2024</v>
@@ -3644,10 +3644,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B104" s="24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C104" s="25">
         <v>3</v>
@@ -3657,7 +3657,7 @@
         <v>36</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F104" s="6">
         <v>2025</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C105" s="34">
         <v>3</v>
@@ -3678,7 +3678,7 @@
         <v>36</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F105" s="6">
         <v>2023</v>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C106" s="30">
         <v>3</v>
@@ -3699,7 +3699,7 @@
         <v>36</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F106" s="6">
         <v>2024</v>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B107" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C107" s="25">
         <v>2</v>
@@ -3720,7 +3720,7 @@
         <v>24</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F107" s="6">
         <v>2025</v>
@@ -3728,10 +3728,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B108" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C108" s="25">
         <v>4</v>
@@ -3741,7 +3741,7 @@
         <v>48</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F108" s="6">
         <v>2025</v>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B109" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C109" s="25">
         <v>4</v>
@@ -3762,7 +3762,7 @@
         <v>48</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F109" s="6">
         <v>2025</v>
@@ -3770,10 +3770,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C110" s="15">
         <v>4</v>
@@ -3783,7 +3783,7 @@
         <v>48</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F110" s="6">
         <v>2024</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C111" s="17">
         <v>3</v>
@@ -3804,7 +3804,7 @@
         <v>36</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F111" s="6">
         <v>2025</v>
@@ -3812,10 +3812,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C112" s="26">
         <v>5</v>
@@ -3825,7 +3825,7 @@
         <v>60</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F112" s="6">
         <v>2022</v>
@@ -3833,10 +3833,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C113" s="17">
         <v>4</v>
@@ -3846,7 +3846,7 @@
         <v>48</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F113" s="6">
         <v>2025</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C114" s="22">
         <v>5</v>
@@ -3867,7 +3867,7 @@
         <v>60</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F114" s="6">
         <v>2023</v>
@@ -3875,10 +3875,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C115" s="15">
         <v>6</v>
@@ -3888,7 +3888,7 @@
         <v>72</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F115" s="6">
         <v>2024</v>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B116" s="24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C116" s="25">
         <v>8</v>
@@ -3909,7 +3909,7 @@
         <v>96</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F116" s="6">
         <v>2025</v>
@@ -3917,10 +3917,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C117" s="19">
         <v>3</v>
@@ -3930,7 +3930,7 @@
         <v>36</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F117" s="6">
         <v>2023</v>
@@ -3938,10 +3938,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C118" s="15">
         <v>8</v>
@@ -3951,7 +3951,7 @@
         <v>96</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F118" s="6">
         <v>2024</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C119" s="19">
         <v>2</v>
@@ -3972,7 +3972,7 @@
         <v>24</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F119" s="6">
         <v>2023</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C120" s="23">
         <v>2</v>
@@ -3993,7 +3993,7 @@
         <v>24</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F120" s="6">
         <v>2022</v>
@@ -4001,10 +4001,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C121" s="15">
         <v>2</v>
@@ -4014,7 +4014,7 @@
         <v>24</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F121" s="6">
         <v>2024</v>
@@ -4022,10 +4022,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B122" s="24" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C122" s="25">
         <v>2</v>
@@ -4035,7 +4035,7 @@
         <v>24</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F122" s="6">
         <v>2025</v>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B123" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C123" s="17">
         <v>3</v>
@@ -4056,7 +4056,7 @@
         <v>36</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F123" s="6">
         <v>2025</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C124" s="15">
         <v>1</v>
@@ -4077,7 +4077,7 @@
         <v>12</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F124" s="6">
         <v>2024</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C125" s="15">
         <v>20</v>
@@ -4098,7 +4098,7 @@
         <v>240</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F125" s="6">
         <v>2024</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B126" s="16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C126" s="17">
         <v>16</v>
@@ -4119,7 +4119,7 @@
         <v>192</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F126" s="6">
         <v>2025</v>
@@ -4127,10 +4127,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C127" s="4">
         <v>2</v>
@@ -4140,7 +4140,7 @@
         <v>24</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F127" s="6">
         <v>2023</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="128" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C128" s="8">
         <v>2</v>
@@ -4161,7 +4161,7 @@
         <v>24</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F128" s="6">
         <v>2022</v>
@@ -4169,10 +4169,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C129" s="12">
         <v>2</v>
@@ -4182,7 +4182,7 @@
         <v>24</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F129" s="6">
         <v>2025</v>
@@ -4190,10 +4190,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C130" s="10">
         <v>2</v>
@@ -4203,7 +4203,7 @@
         <v>24</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F130" s="6">
         <v>2024</v>
@@ -4211,10 +4211,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C131" s="4">
         <v>2</v>
@@ -4224,7 +4224,7 @@
         <v>24</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F131" s="6">
         <v>2023</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="132" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C132" s="8">
         <v>2</v>
@@ -4245,7 +4245,7 @@
         <v>24</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F132" s="6">
         <v>2022</v>
@@ -4253,10 +4253,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C133" s="10">
         <v>2</v>
@@ -4266,7 +4266,7 @@
         <v>24</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F133" s="6">
         <v>2024</v>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C134" s="28">
         <v>2</v>
@@ -4287,7 +4287,7 @@
         <v>24</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F134" s="6">
         <v>2025</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C135" s="4">
         <v>12</v>
@@ -4308,7 +4308,7 @@
         <v>144</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F135" s="6">
         <v>2023</v>
@@ -4316,10 +4316,10 @@
     </row>
     <row r="136" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C136" s="8">
         <v>12</v>
@@ -4329,7 +4329,7 @@
         <v>144</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F136" s="6">
         <v>2022</v>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C137" s="10">
         <v>24</v>
@@ -4350,7 +4350,7 @@
         <v>288</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F137" s="6">
         <v>2024</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C138" s="28">
         <v>18</v>
@@ -4371,7 +4371,7 @@
         <v>216</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F138" s="6">
         <v>2025</v>
@@ -4379,10 +4379,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B139" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C139" s="25">
         <v>2</v>
@@ -4392,7 +4392,7 @@
         <v>24</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F139" s="6">
         <v>2025</v>
@@ -4400,10 +4400,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C140" s="19">
         <v>1</v>
@@ -4413,7 +4413,7 @@
         <v>12</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F140" s="6">
         <v>2023</v>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C141" s="26">
         <v>1</v>
@@ -4434,7 +4434,7 @@
         <v>12</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F141" s="6">
         <v>2022</v>
@@ -4442,10 +4442,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C142" s="15">
         <v>3</v>
@@ -4455,7 +4455,7 @@
         <v>36</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F142" s="6">
         <v>2024</v>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C143" s="15">
         <v>8</v>
@@ -4476,7 +4476,7 @@
         <v>96</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F143" s="6">
         <v>2024</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B144" s="16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C144" s="17">
         <v>6</v>
@@ -4497,7 +4497,7 @@
         <v>72</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F144" s="6">
         <v>2025</v>
@@ -4505,10 +4505,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C145" s="34">
         <v>5</v>
@@ -4518,7 +4518,7 @@
         <v>60</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F145" s="6">
         <v>2023</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C146" s="26">
         <v>5</v>
@@ -4539,7 +4539,7 @@
         <v>60</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F146" s="6">
         <v>2022</v>
@@ -4547,10 +4547,10 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C147" s="4">
         <v>6</v>
@@ -4560,7 +4560,7 @@
         <v>72</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F147" s="6">
         <v>2023</v>
@@ -4568,10 +4568,10 @@
     </row>
     <row r="148" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C148" s="8">
         <v>6</v>
@@ -4581,7 +4581,7 @@
         <v>72</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F148" s="6">
         <v>2022</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C149" s="36">
         <v>4</v>
@@ -4602,7 +4602,7 @@
         <v>48</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F149" s="6">
         <v>2025</v>
@@ -4610,10 +4610,10 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C150" s="32">
         <v>1</v>
@@ -4622,7 +4622,7 @@
         <v>12</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F150" s="6">
         <v>2024</v>
@@ -4630,10 +4630,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="24" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B151" s="24" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C151" s="25">
         <v>1</v>
@@ -4643,7 +4643,7 @@
         <v>12</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F151" s="6">
         <v>2025</v>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C152" s="19">
         <v>6</v>
@@ -4664,7 +4664,7 @@
         <v>72</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F152" s="6">
         <v>2023</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C153" s="26">
         <v>12</v>
@@ -4685,7 +4685,7 @@
         <v>144</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F153" s="6">
         <v>2022</v>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C154" s="34">
         <v>1</v>
@@ -4706,7 +4706,7 @@
         <v>12</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F154" s="6">
         <v>2023</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C155" s="34">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>120</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F155" s="6">
         <v>2023</v>
@@ -4735,10 +4735,10 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C156" s="15">
         <v>30</v>
@@ -4748,7 +4748,7 @@
         <v>360</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F156" s="6">
         <v>2024</v>
@@ -4756,10 +4756,10 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C157" s="34">
         <v>4</v>
@@ -4769,7 +4769,7 @@
         <v>48</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F157" s="6">
         <v>2023</v>
@@ -4777,10 +4777,10 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B158" s="24" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C158" s="25">
         <v>40</v>
@@ -4790,7 +4790,7 @@
         <v>480</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F158" s="6">
         <v>2025</v>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C159" s="15">
         <v>6</v>
@@ -4811,7 +4811,7 @@
         <v>72</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F159" s="6">
         <v>2024</v>
@@ -4819,10 +4819,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B160" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C160" s="17">
         <v>6</v>
@@ -4832,7 +4832,7 @@
         <v>72</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F160" s="6">
         <v>2025</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B161" s="16" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C161" s="17">
         <v>20</v>
@@ -4853,7 +4853,7 @@
         <v>240</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F161" s="6">
         <v>2025</v>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C162" s="34">
         <v>13</v>
@@ -4874,7 +4874,7 @@
         <v>156</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F162" s="6">
         <v>2023</v>
@@ -4882,10 +4882,10 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C163" s="26">
         <v>12</v>
@@ -4895,7 +4895,7 @@
         <v>144</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F163" s="6">
         <v>2022</v>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C164" s="15">
         <v>20</v>
@@ -4916,7 +4916,7 @@
         <v>240</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F164" s="6">
         <v>2024</v>
@@ -4924,10 +4924,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B165" s="24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C165" s="25">
         <v>2</v>
@@ -4937,7 +4937,7 @@
         <v>24</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F165" s="6">
         <v>2025</v>
@@ -4945,10 +4945,10 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C166" s="26">
         <v>1</v>
@@ -4958,7 +4958,7 @@
         <v>12</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F166" s="6">
         <v>2024</v>
@@ -4966,10 +4966,10 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B167" s="16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C167" s="17">
         <v>1</v>
@@ -4979,7 +4979,7 @@
         <v>12</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F167" s="6">
         <v>2025</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C168" s="34">
         <v>3</v>
@@ -5000,7 +5000,7 @@
         <v>36</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F168" s="6">
         <v>2023</v>
@@ -5008,10 +5008,10 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C169" s="26">
         <v>3</v>
@@ -5021,7 +5021,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F169" s="6">
         <v>2022</v>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C170" s="15">
         <v>4</v>
@@ -5042,7 +5042,7 @@
         <v>48</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F170" s="6">
         <v>2024</v>
@@ -5050,10 +5050,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B171" s="16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C171" s="17">
         <v>3</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F171" s="6">
         <v>2025</v>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B172" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C172" s="29">
         <v>2</v>
@@ -5084,7 +5084,7 @@
         <v>24</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F172" s="6">
         <v>2022</v>
@@ -5092,10 +5092,10 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B173" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C173" s="22">
         <v>4</v>
@@ -5105,7 +5105,7 @@
         <v>48</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F173" s="6">
         <v>2023</v>
@@ -5113,10 +5113,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B174" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C174" s="30">
         <v>8</v>
@@ -5126,7 +5126,7 @@
         <v>96</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F174" s="6">
         <v>2024</v>
@@ -5134,10 +5134,10 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B175" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C175" s="17">
         <v>6</v>
@@ -5147,7 +5147,7 @@
         <v>72</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F175" s="6">
         <v>2025</v>
@@ -5155,10 +5155,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C176" s="34">
         <v>2</v>
@@ -5168,7 +5168,7 @@
         <v>24</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F176" s="6">
         <v>2023</v>
@@ -5176,10 +5176,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B177" s="16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C177" s="17">
         <v>3</v>
@@ -5189,7 +5189,7 @@
         <v>36</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F177" s="6">
         <v>2025</v>
@@ -5197,10 +5197,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C178" s="29">
         <v>2</v>
@@ -5210,7 +5210,7 @@
         <v>24</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F178" s="6">
         <v>2022</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B179" s="11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C179" s="30">
         <v>4</v>
@@ -5231,7 +5231,7 @@
         <v>48</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F179" s="6">
         <v>2024</v>
@@ -5239,10 +5239,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C180" s="30">
         <v>10</v>
@@ -5252,7 +5252,7 @@
         <v>120</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F180" s="6">
         <v>2024</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B181" s="16" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C181" s="17">
         <v>12</v>
@@ -5273,7 +5273,7 @@
         <v>144</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F181" s="6">
         <v>2025</v>
@@ -5281,10 +5281,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B182" s="16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C182" s="17">
         <v>3</v>
@@ -5294,7 +5294,7 @@
         <v>36</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F182" s="6">
         <v>2025</v>
@@ -5302,10 +5302,10 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C183" s="34">
         <v>1</v>
@@ -5315,7 +5315,7 @@
         <v>12</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F183" s="6">
         <v>2023</v>
@@ -5323,10 +5323,10 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B184" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C184" s="29">
         <v>1</v>
@@ -5336,7 +5336,7 @@
         <v>12</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F184" s="6">
         <v>2022</v>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B185" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C185" s="30">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         <v>24</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F185" s="6">
         <v>2024</v>
@@ -5365,10 +5365,10 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C186" s="29">
         <v>2</v>
@@ -5378,7 +5378,7 @@
         <v>24</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F186" s="6">
         <v>2022</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C187" s="34">
         <v>2</v>
@@ -5399,7 +5399,7 @@
         <v>24</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F187" s="6">
         <v>2023</v>
@@ -5407,10 +5407,10 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B188" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C188" s="25">
         <v>2</v>
@@ -5420,7 +5420,7 @@
         <v>24</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F188" s="6">
         <v>2025</v>
@@ -5428,10 +5428,10 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C189" s="30">
         <v>5</v>
@@ -5441,7 +5441,7 @@
         <v>60</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F189" s="6">
         <v>2024</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="16" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B190" s="16" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C190" s="17">
         <v>3</v>
@@ -5462,7 +5462,7 @@
         <v>36</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F190" s="6">
         <v>2025</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C191" s="19">
         <v>2</v>
@@ -5483,7 +5483,7 @@
         <v>24</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F191" s="6">
         <v>2023</v>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C192" s="26">
         <v>2</v>
@@ -5504,7 +5504,7 @@
         <v>24</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F192" s="6">
         <v>2022</v>
@@ -5512,10 +5512,10 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B193" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C193" s="15">
         <v>3</v>
@@ -5525,7 +5525,7 @@
         <v>36</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F193" s="6">
         <v>2024</v>
@@ -5533,10 +5533,10 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B194" s="21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C194" s="31">
         <v>10</v>
@@ -5546,7 +5546,7 @@
         <v>120</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F194" s="6">
         <v>2023</v>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C195" s="23">
         <v>10</v>
@@ -5567,7 +5567,7 @@
         <v>120</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F195" s="6">
         <v>2022</v>
@@ -5575,10 +5575,10 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C196" s="32">
         <v>10</v>
@@ -5587,7 +5587,7 @@
         <v>120</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F196" s="6">
         <v>2024</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C197" s="28">
         <v>7</v>
@@ -5608,7 +5608,7 @@
         <v>84</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F197" s="6">
         <v>2025</v>
@@ -5616,10 +5616,10 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="16" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B198" s="16" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C198" s="17">
         <v>10</v>
@@ -5629,7 +5629,7 @@
         <v>120</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F198" s="6">
         <v>2025</v>
@@ -5637,10 +5637,10 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C199" s="19">
         <v>7</v>
@@ -5650,7 +5650,7 @@
         <v>84</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F199" s="6">
         <v>2023</v>
@@ -5658,10 +5658,10 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C200" s="13">
         <v>6</v>
@@ -5671,7 +5671,7 @@
         <v>72</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F200" s="6">
         <v>2022</v>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C201" s="15">
         <v>10</v>
@@ -5692,7 +5692,7 @@
         <v>120</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F201" s="6">
         <v>2024</v>
@@ -5700,10 +5700,10 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C202" s="15">
         <v>1</v>
@@ -5713,7 +5713,7 @@
         <v>12</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F202" s="6">
         <v>2024</v>
@@ -5721,10 +5721,10 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="16" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B203" s="16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C203" s="17">
         <v>1</v>
@@ -5734,7 +5734,7 @@
         <v>12</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F203" s="6">
         <v>2025</v>
@@ -5742,10 +5742,10 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B204" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C204" s="17">
         <v>13</v>
@@ -5755,7 +5755,7 @@
         <v>156</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F204" s="6">
         <v>2025</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C205" s="34">
         <v>8</v>
@@ -5776,7 +5776,7 @@
         <v>96</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F205" s="6">
         <v>2023</v>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C206" s="13">
         <v>4</v>
@@ -5797,7 +5797,7 @@
         <v>48</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F206" s="6">
         <v>2022</v>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C207" s="15">
         <v>12</v>
@@ -5818,7 +5818,7 @@
         <v>144</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F207" s="6">
         <v>2024</v>
@@ -5826,10 +5826,10 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B208" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C208" s="17">
         <v>3</v>
@@ -5839,7 +5839,7 @@
         <v>36</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F208" s="6">
         <v>2025</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C209" s="34">
         <v>2</v>
@@ -5860,7 +5860,7 @@
         <v>24</v>
       </c>
       <c r="E209" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F209" s="6">
         <v>2023</v>
@@ -5868,10 +5868,10 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C210" s="13">
         <v>2</v>
@@ -5881,7 +5881,7 @@
         <v>24</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F210" s="6">
         <v>2022</v>
@@ -5889,10 +5889,10 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C211" s="15">
         <v>3</v>
@@ -5902,7 +5902,7 @@
         <v>36</v>
       </c>
       <c r="E211" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F211" s="6">
         <v>2024</v>
@@ -5910,10 +5910,10 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C212" s="23">
         <v>4</v>
@@ -5923,7 +5923,7 @@
         <v>48</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F212" s="6">
         <v>2022</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C213" s="19">
         <v>6</v>
@@ -5944,7 +5944,7 @@
         <v>72</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F213" s="6">
         <v>2023</v>
@@ -5952,10 +5952,10 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C214" s="13">
         <v>6</v>
@@ -5965,7 +5965,7 @@
         <v>72</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F214" s="6">
         <v>2022</v>
@@ -5973,10 +5973,10 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B215" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C215" s="15">
         <v>6</v>
@@ -5986,7 +5986,7 @@
         <v>72</v>
       </c>
       <c r="E215" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F215" s="6">
         <v>2024</v>
@@ -5994,10 +5994,10 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B216" s="24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C216" s="25">
         <v>1</v>
@@ -6007,7 +6007,7 @@
         <v>12</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F216" s="6">
         <v>2025</v>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C217" s="15">
         <v>1</v>
@@ -6028,7 +6028,7 @@
         <v>12</v>
       </c>
       <c r="E217" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F217" s="6">
         <v>2024</v>
@@ -6036,10 +6036,10 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B218" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C218" s="17">
         <v>1</v>
@@ -6049,7 +6049,7 @@
         <v>12</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F218" s="6">
         <v>2025</v>
@@ -6057,10 +6057,10 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C219" s="4">
         <v>3</v>
@@ -6070,7 +6070,7 @@
         <v>36</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F219" s="6">
         <v>2023</v>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="220" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C220" s="8">
         <v>3</v>
@@ -6091,7 +6091,7 @@
         <v>36</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F220" s="6">
         <v>2022</v>
@@ -6099,10 +6099,10 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C221" s="10">
         <v>3</v>
@@ -6112,7 +6112,7 @@
         <v>36</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F221" s="6">
         <v>2024</v>
@@ -6120,10 +6120,10 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B222" s="11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C222" s="12">
         <v>4</v>
@@ -6133,7 +6133,7 @@
         <v>48</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F222" s="6">
         <v>2025</v>
@@ -6141,10 +6141,10 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="24" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B223" s="24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C223" s="25">
         <v>1</v>
@@ -6154,7 +6154,7 @@
         <v>12</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F223" s="6">
         <v>2025</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C224" s="28">
         <v>16</v>
@@ -6175,7 +6175,7 @@
         <v>192</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F224" s="6">
         <v>2025</v>
@@ -6183,10 +6183,10 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C225" s="4">
         <v>5</v>
@@ -6196,7 +6196,7 @@
         <v>60</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F225" s="6">
         <v>2023</v>
@@ -6204,10 +6204,10 @@
     </row>
     <row r="226" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C226" s="8">
         <v>5</v>
@@ -6217,7 +6217,7 @@
         <v>60</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F226" s="6">
         <v>2022</v>
@@ -6225,10 +6225,10 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C227" s="10">
         <v>15</v>
@@ -6238,7 +6238,7 @@
         <v>180</v>
       </c>
       <c r="E227" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F227" s="6">
         <v>2024</v>
@@ -6246,10 +6246,10 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C228" s="4">
         <v>4</v>
@@ -6259,7 +6259,7 @@
         <v>48</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F228" s="6">
         <v>2023</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="229" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C229" s="8">
         <v>4</v>
@@ -6280,7 +6280,7 @@
         <v>48</v>
       </c>
       <c r="E229" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F229" s="6">
         <v>2022</v>
@@ -6288,10 +6288,10 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C230" s="10">
         <v>6</v>
@@ -6301,7 +6301,7 @@
         <v>72</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F230" s="6">
         <v>2024</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B231" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C231" s="12">
         <v>3.5</v>
@@ -6322,7 +6322,7 @@
         <v>42</v>
       </c>
       <c r="E231" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F231" s="6">
         <v>2025</v>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B232" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C232" s="12">
         <v>2</v>
@@ -6343,7 +6343,7 @@
         <v>24</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F232" s="6">
         <v>2025</v>
@@ -6351,10 +6351,10 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B233" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C233" s="15">
         <v>1</v>
@@ -6364,7 +6364,7 @@
         <v>12</v>
       </c>
       <c r="E233" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F233" s="6">
         <v>2024</v>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="16" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B234" s="16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C234" s="17">
         <v>1</v>
@@ -6385,7 +6385,7 @@
         <v>12</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F234" s="6">
         <v>2025</v>
@@ -6393,10 +6393,10 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B235" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C235" s="12">
         <v>3</v>
@@ -6406,7 +6406,7 @@
         <v>36</v>
       </c>
       <c r="E235" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F235" s="6">
         <v>2025</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C236" s="10">
         <v>4</v>
@@ -6427,7 +6427,7 @@
         <v>48</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F236" s="6">
         <v>2024</v>
@@ -6435,10 +6435,10 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C237" s="4">
         <v>4</v>
@@ -6448,7 +6448,7 @@
         <v>48</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F237" s="6">
         <v>2023</v>
@@ -6456,10 +6456,10 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B238" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C238" s="15">
         <v>3</v>
@@ -6469,7 +6469,7 @@
         <v>36</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F238" s="6">
         <v>2024</v>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="16" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B239" s="16" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C239" s="17">
         <v>2</v>
@@ -6490,7 +6490,7 @@
         <v>24</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F239" s="6">
         <v>2025</v>
@@ -6498,10 +6498,10 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C240" s="13">
         <v>2</v>
@@ -6511,7 +6511,7 @@
         <v>24</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F240" s="6">
         <v>2022</v>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B241" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C241" s="19">
         <v>4</v>
@@ -6532,7 +6532,7 @@
         <v>48</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F241" s="6">
         <v>2023</v>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B242" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C242" s="15">
         <v>3</v>
@@ -6553,7 +6553,7 @@
         <v>36</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F242" s="6">
         <v>2024</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="16" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B243" s="16" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C243" s="17">
         <v>2</v>
@@ -6574,7 +6574,7 @@
         <v>24</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F243" s="6">
         <v>2025</v>
@@ -6582,10 +6582,10 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B244" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C244" s="12">
         <v>4</v>
@@ -6595,7 +6595,7 @@
         <v>48</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F244" s="6">
         <v>2025</v>
@@ -6603,10 +6603,10 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C245" s="4">
         <v>2</v>
@@ -6616,7 +6616,7 @@
         <v>24</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F245" s="6">
         <v>2023</v>
@@ -6624,10 +6624,10 @@
     </row>
     <row r="246" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C246" s="8">
         <v>3</v>
@@ -6637,7 +6637,7 @@
         <v>36</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F246" s="6">
         <v>2022</v>
@@ -6645,10 +6645,10 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B247" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C247" s="10">
         <v>2</v>
@@ -6658,7 +6658,7 @@
         <v>24</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F247" s="6">
         <v>2024</v>
@@ -6666,10 +6666,10 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C248" s="10">
         <v>6</v>
@@ -6679,7 +6679,7 @@
         <v>72</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F248" s="6">
         <v>2024</v>
@@ -6687,10 +6687,10 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C249" s="12">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>36</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F249" s="6">
         <v>2025</v>
@@ -6708,10 +6708,10 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B250" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C250" s="12">
         <v>3</v>
@@ -6721,7 +6721,7 @@
         <v>36</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F250" s="6">
         <v>2025</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C251" s="4">
         <v>3</v>
@@ -6742,7 +6742,7 @@
         <v>36</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F251" s="6">
         <v>2023</v>
@@ -6750,10 +6750,10 @@
     </row>
     <row r="252" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C252" s="8">
         <v>3</v>
@@ -6763,7 +6763,7 @@
         <v>36</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F252" s="6">
         <v>2022</v>
@@ -6771,10 +6771,10 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C253" s="10">
         <v>3</v>
@@ -6784,7 +6784,7 @@
         <v>36</v>
       </c>
       <c r="E253" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F253" s="6">
         <v>2024</v>
@@ -6792,10 +6792,10 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B254" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C254" s="17">
         <v>3</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F254" s="6">
         <v>2025</v>
@@ -6813,10 +6813,10 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C255" s="34">
         <v>1</v>
@@ -6826,7 +6826,7 @@
         <v>12</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F255" s="6">
         <v>2023</v>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C256" s="13">
         <v>3</v>
@@ -6847,7 +6847,7 @@
         <v>36</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F256" s="6">
         <v>2022</v>
@@ -6855,10 +6855,10 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B257" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C257" s="38">
         <v>1</v>
@@ -6868,7 +6868,7 @@
         <v>12</v>
       </c>
       <c r="E257" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F257" s="6">
         <v>2024</v>
@@ -6876,10 +6876,10 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C258" s="28">
         <v>14</v>
@@ -6889,7 +6889,7 @@
         <v>168</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F258" s="6">
         <v>2025</v>
@@ -6897,10 +6897,10 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C259" s="12">
         <v>1</v>
@@ -6910,7 +6910,7 @@
         <v>12</v>
       </c>
       <c r="E259" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F259" s="6">
         <v>2025</v>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C260" s="4">
         <v>2</v>
@@ -6931,7 +6931,7 @@
         <v>24</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F260" s="6">
         <v>2023</v>
@@ -6939,10 +6939,10 @@
     </row>
     <row r="261" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C261" s="8">
         <v>2</v>
@@ -6952,7 +6952,7 @@
         <v>24</v>
       </c>
       <c r="E261" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F261" s="6">
         <v>2022</v>
@@ -6960,10 +6960,10 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B262" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C262" s="10">
         <v>3</v>
@@ -6973,7 +6973,7 @@
         <v>36</v>
       </c>
       <c r="E262" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F262" s="6">
         <v>2024</v>
@@ -6981,10 +6981,10 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B263" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C263" s="32">
         <v>4</v>
@@ -6993,7 +6993,7 @@
         <v>48</v>
       </c>
       <c r="E263" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F263" s="6">
         <v>2024</v>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B264" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C264" s="12">
         <v>2</v>
@@ -7014,7 +7014,7 @@
         <v>24</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F264" s="6">
         <v>2025</v>
@@ -7022,10 +7022,10 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B265" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C265" s="17">
         <v>2</v>
@@ -7035,7 +7035,7 @@
         <v>24</v>
       </c>
       <c r="E265" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F265" s="6">
         <v>2025</v>
@@ -7043,10 +7043,10 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B266" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C266" s="34">
         <v>1</v>
@@ -7056,7 +7056,7 @@
         <v>12</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F266" s="6">
         <v>2023</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C267" s="13">
         <v>2</v>
@@ -7077,7 +7077,7 @@
         <v>24</v>
       </c>
       <c r="E267" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F267" s="6">
         <v>2022</v>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C268" s="38">
         <v>2</v>
@@ -7098,7 +7098,7 @@
         <v>24</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F268" s="6">
         <v>2024</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B269" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C269" s="19">
         <v>20</v>
@@ -7119,7 +7119,7 @@
         <v>240</v>
       </c>
       <c r="E269" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F269" s="6">
         <v>2023</v>
@@ -7127,10 +7127,10 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B270" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C270" s="23">
         <v>10</v>
@@ -7140,7 +7140,7 @@
         <v>120</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F270" s="6">
         <v>2022</v>
@@ -7148,10 +7148,10 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B271" s="16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C271" s="17">
         <v>16</v>
@@ -7161,7 +7161,7 @@
         <v>192</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F271" s="6">
         <v>2025</v>
@@ -7169,10 +7169,10 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B272" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C272" s="38">
         <v>15</v>
@@ -7182,7 +7182,7 @@
         <v>180</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F272" s="6">
         <v>2024</v>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B273" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C273" s="19">
         <v>1</v>
@@ -7203,7 +7203,7 @@
         <v>12</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F273" s="6">
         <v>2023</v>
@@ -7211,10 +7211,10 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B274" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C274" s="23">
         <v>2</v>
@@ -7224,7 +7224,7 @@
         <v>24</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F274" s="6">
         <v>2022</v>
@@ -7232,10 +7232,10 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B275" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C275" s="38">
         <v>2</v>
@@ -7245,7 +7245,7 @@
         <v>24</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F275" s="6">
         <v>2024</v>
@@ -7253,10 +7253,10 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B276" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C276" s="17">
         <v>2</v>
@@ -7266,7 +7266,7 @@
         <v>24</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F276" s="6">
         <v>2025</v>
@@ -7274,10 +7274,10 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B277" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C277" s="19">
         <v>10</v>
@@ -7287,7 +7287,7 @@
         <v>120</v>
       </c>
       <c r="E277" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F277" s="6">
         <v>2023</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C278" s="23">
         <v>6</v>
@@ -7308,7 +7308,7 @@
         <v>72</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F278" s="6">
         <v>2022</v>
@@ -7316,10 +7316,10 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C279" s="19">
         <v>2</v>
@@ -7329,7 +7329,7 @@
         <v>24</v>
       </c>
       <c r="E279" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F279" s="6">
         <v>2023</v>
@@ -7337,10 +7337,10 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B280" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C280" s="23">
         <v>2</v>
@@ -7350,7 +7350,7 @@
         <v>24</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F280" s="6">
         <v>2022</v>
@@ -7358,10 +7358,10 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B281" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C281" s="19">
         <v>2</v>
@@ -7371,7 +7371,7 @@
         <v>24</v>
       </c>
       <c r="E281" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F281" s="6">
         <v>2023</v>
@@ -7379,10 +7379,10 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B282" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C282" s="40">
         <v>2</v>
@@ -7392,7 +7392,7 @@
         <v>24</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F282" s="6">
         <v>2022</v>
@@ -7400,10 +7400,10 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B283" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C283" s="17">
         <v>3</v>
@@ -7413,7 +7413,7 @@
         <v>36</v>
       </c>
       <c r="E283" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F283" s="6">
         <v>2025</v>
@@ -7421,10 +7421,10 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B284" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C284" s="17">
         <v>4</v>
@@ -7434,7 +7434,7 @@
         <v>48</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F284" s="6">
         <v>2025</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="41" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B285" s="41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C285" s="23">
         <v>6</v>
@@ -7455,7 +7455,7 @@
         <v>72</v>
       </c>
       <c r="E285" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F285" s="6">
         <v>2024</v>
@@ -7463,10 +7463,10 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B286" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C286" s="23">
         <v>1</v>
@@ -7476,7 +7476,7 @@
         <v>12</v>
       </c>
       <c r="E286" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F286" s="6">
         <v>2022</v>
@@ -7484,10 +7484,10 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="41" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B287" s="41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C287" s="23">
         <v>1</v>
@@ -7497,7 +7497,7 @@
         <v>12</v>
       </c>
       <c r="E287" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F287" s="6">
         <v>2024</v>
@@ -7505,10 +7505,10 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="16" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B288" s="16" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C288" s="17">
         <v>1</v>
@@ -7518,7 +7518,7 @@
         <v>12</v>
       </c>
       <c r="E288" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F288" s="6">
         <v>2025</v>
@@ -7526,10 +7526,10 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B289" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C289" s="17">
         <v>2</v>
@@ -7539,7 +7539,7 @@
         <v>24</v>
       </c>
       <c r="E289" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F289" s="6">
         <v>2025</v>
@@ -7547,10 +7547,10 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="41" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B290" s="41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C290" s="38">
         <v>2</v>
@@ -7560,7 +7560,7 @@
         <v>24</v>
       </c>
       <c r="E290" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F290" s="6">
         <v>2024</v>
@@ -7568,10 +7568,10 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C291" s="12">
         <v>2</v>
@@ -7581,7 +7581,7 @@
         <v>24</v>
       </c>
       <c r="E291" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F291" s="6">
         <v>2025</v>
@@ -7589,10 +7589,10 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C292" s="4">
         <v>4</v>
@@ -7602,7 +7602,7 @@
         <v>48</v>
       </c>
       <c r="E292" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F292" s="6">
         <v>2023</v>
@@ -7610,10 +7610,10 @@
     </row>
     <row r="293" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B293" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C293" s="8">
         <v>4</v>
@@ -7623,7 +7623,7 @@
         <v>48</v>
       </c>
       <c r="E293" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F293" s="6">
         <v>2022</v>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B294" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C294" s="10">
         <v>4</v>
@@ -7644,7 +7644,7 @@
         <v>48</v>
       </c>
       <c r="E294" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F294" s="6">
         <v>2024</v>
@@ -7652,10 +7652,10 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C295" s="4">
         <v>3</v>
@@ -7665,7 +7665,7 @@
         <v>36</v>
       </c>
       <c r="E295" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F295" s="6">
         <v>2023</v>
@@ -7673,10 +7673,10 @@
     </row>
     <row r="296" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B296" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C296" s="8">
         <v>3</v>
@@ -7686,7 +7686,7 @@
         <v>36</v>
       </c>
       <c r="E296" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F296" s="6">
         <v>2022</v>
@@ -7694,10 +7694,10 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="11" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B297" s="11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C297" s="12">
         <v>3</v>
@@ -7707,7 +7707,7 @@
         <v>36</v>
       </c>
       <c r="E297" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F297" s="6">
         <v>2025</v>
@@ -7715,10 +7715,10 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B298" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C298" s="10">
         <v>6</v>
@@ -7728,7 +7728,7 @@
         <v>72</v>
       </c>
       <c r="E298" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F298" s="6">
         <v>2024</v>
@@ -7736,10 +7736,10 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B299" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C299" s="28">
         <v>24</v>
@@ -7749,7 +7749,7 @@
         <v>288</v>
       </c>
       <c r="E299" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F299" s="6">
         <v>2025</v>
